--- a/outputs/rebuilt_excels/build_rogue_system_reference.xlsx
+++ b/outputs/rebuilt_excels/build_rogue_system_reference.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="1" r:id="Rb20be797034c4831"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="伤害系统" sheetId="2" r:id="Ra57af3dea62943b0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="经济系统" sheetId="3" r:id="R08349aa6f67d4474"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="关卡成长" sheetId="4" r:id="R0abc8e58cec842ce"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="羁绊说明" sheetId="5" r:id="Rfc7bfca95db04669"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="字段字典" sheetId="6" r:id="Re0d25b9eb73c4f3e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="天命奇遇效果索引" sheetId="7" r:id="Rec8ae949c3c54cb0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="1" r:id="R3dcc89cd8789460e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="伤害系统" sheetId="2" r:id="Rb6504e10203a4f89"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="经济系统" sheetId="3" r:id="R1485300636e14a35"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="关卡成长" sheetId="4" r:id="Re85fbe1c264043af"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="羁绊说明" sheetId="5" r:id="Rc47746995a6e47d8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="字段字典" sheetId="6" r:id="R1b893292886440ca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="天命奇遇效果索引" sheetId="7" r:id="R654dfea34ee64a47"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -429,7 +429,7 @@
         <x:v>生成时间</x:v>
       </x:c>
       <x:c r="B3" s="5" t="n">
-        <x:v>46200.64384505787</x:v>
+        <x:v>46200.783423472225</x:v>
       </x:c>
     </x:row>
     <x:row r="4">

--- a/outputs/rebuilt_excels/build_rogue_system_reference.xlsx
+++ b/outputs/rebuilt_excels/build_rogue_system_reference.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="1" r:id="R3dcc89cd8789460e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="伤害系统" sheetId="2" r:id="Rb6504e10203a4f89"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="经济系统" sheetId="3" r:id="R1485300636e14a35"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="关卡成长" sheetId="4" r:id="Re85fbe1c264043af"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="羁绊说明" sheetId="5" r:id="Rc47746995a6e47d8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="字段字典" sheetId="6" r:id="R1b893292886440ca"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="天命奇遇效果索引" sheetId="7" r:id="R654dfea34ee64a47"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="1" r:id="R717e6fd974494ac0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="伤害系统" sheetId="2" r:id="Ra15d56dd3e7a461c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="经济系统" sheetId="3" r:id="Rbdaf19d88db34a36"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="关卡成长" sheetId="4" r:id="R9e871a4486304821"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="羁绊说明" sheetId="5" r:id="R0587959917244df5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="字段字典" sheetId="6" r:id="R4d826c94d6e549b2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="天命奇遇效果索引" sheetId="7" r:id="R99869510173545a3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -429,7 +429,7 @@
         <x:v>生成时间</x:v>
       </x:c>
       <x:c r="B3" s="5" t="n">
-        <x:v>46200.783423472225</x:v>
+        <x:v>46200.794970856485</x:v>
       </x:c>
     </x:row>
     <x:row r="4">

--- a/outputs/rebuilt_excels/build_rogue_system_reference.xlsx
+++ b/outputs/rebuilt_excels/build_rogue_system_reference.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="1" r:id="R717e6fd974494ac0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="伤害系统" sheetId="2" r:id="Ra15d56dd3e7a461c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="经济系统" sheetId="3" r:id="Rbdaf19d88db34a36"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="关卡成长" sheetId="4" r:id="R9e871a4486304821"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="羁绊说明" sheetId="5" r:id="R0587959917244df5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="字段字典" sheetId="6" r:id="R4d826c94d6e549b2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="天命奇遇效果索引" sheetId="7" r:id="R99869510173545a3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="1" r:id="Rca3c3ee4e95e45dc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="伤害系统" sheetId="2" r:id="Ra296b876d53c4ffc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="经济系统" sheetId="3" r:id="R41522c7cd01b4a60"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="关卡成长" sheetId="4" r:id="Rb6b758891d2c4f90"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="羁绊说明" sheetId="5" r:id="R04001078a4a040e3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="字段字典" sheetId="6" r:id="Rfd9b63875d5b47c0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="天命奇遇效果索引" sheetId="7" r:id="R23d935e5e09f4ca4"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -429,7 +429,7 @@
         <x:v>生成时间</x:v>
       </x:c>
       <x:c r="B3" s="5" t="n">
-        <x:v>46200.794970856485</x:v>
+        <x:v>46200.80714304398</x:v>
       </x:c>
     </x:row>
     <x:row r="4">

--- a/outputs/rebuilt_excels/build_rogue_system_reference.xlsx
+++ b/outputs/rebuilt_excels/build_rogue_system_reference.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="1" r:id="Rca3c3ee4e95e45dc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="伤害系统" sheetId="2" r:id="Ra296b876d53c4ffc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="经济系统" sheetId="3" r:id="R41522c7cd01b4a60"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="关卡成长" sheetId="4" r:id="Rb6b758891d2c4f90"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="羁绊说明" sheetId="5" r:id="R04001078a4a040e3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="字段字典" sheetId="6" r:id="Rfd9b63875d5b47c0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="天命奇遇效果索引" sheetId="7" r:id="R23d935e5e09f4ca4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="1" r:id="R8e429f8be9da4f10"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="伤害系统" sheetId="2" r:id="R0539c96e840f44ac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="经济系统" sheetId="3" r:id="R64e1c56f71c94c8b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="关卡成长" sheetId="4" r:id="R6ca8bd4dd9cc4eec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="羁绊说明" sheetId="5" r:id="R70b5bb000b834153"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="字段字典" sheetId="6" r:id="R0d58f630cf0a4c0c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="天命奇遇效果索引" sheetId="7" r:id="R24dcbd1739aa4d68"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -429,7 +429,7 @@
         <x:v>生成时间</x:v>
       </x:c>
       <x:c r="B3" s="5" t="n">
-        <x:v>46200.80714304398</x:v>
+        <x:v>46200.98272409722</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -1991,7 +1991,7 @@
         <x:v>法宝</x:v>
       </x:c>
       <x:c r="C8" s="15" t="str">
-        <x:v>特殊效果类型：damage/slow/attack_speed/heal/shield/damage_reduction/counter_damage/avatar_slam。</x:v>
+        <x:v>特殊效果类型：damage/slow/attack_speed/heal/shield/damage_reduction/avatar_slam。</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="34.5" hidden="0" customHeight="1">
